--- a/p/d-ops/az-dops/dtbr-az/topic-list_DtBrk.xlsx
+++ b/p/d-ops/az-dops/dtbr-az/topic-list_DtBrk.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\code\node-refresh\p\d-ops\az-dops\dtbr-az\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B9D6287-0433-466C-9970-762237E6F8E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17600" tabRatio="698" activeTab="6"/>
+    <workbookView xWindow="-28920" yWindow="16185" windowWidth="29040" windowHeight="15720" tabRatio="698" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="what-how" sheetId="21" r:id="rId1"/>
@@ -1402,139 +1408,10 @@
     <t>Procedural data processing follows a structured approach where explicit steps are defined to manipulate data. This model is closely aligned with imperative programming, emphasizing a command sequence that dictates how the data should be processed.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Characteristics</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> of procedural processing:
-Step-by-step execution: The developer explicitly defines the order of operations.
-Use of control structures: Loops, conditionals, and functions manage execution flow.
-Detailed resource control: Enables fine-grained optimizations and manual performance tuning.
-Related concepts: Procedural programming is a sub-class of imperative programming.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Use cases</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> for procedural processing:
-Custom ETL pipelines requiring procedural logic.
-Low-level performance optimizations in batch and streaming workflows.
-Legacy systems or existing imperative scripts.</t>
-    </r>
-  </si>
-  <si>
     <t>Declarative data processing</t>
   </si>
   <si>
     <t>Declarative data processing abstracts the how and focuses on defining the desired result. Instead of specifying step-by-step instructions, developers define transformation logic, and the system determines the most efficient execution plan.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Characteristics</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> of declarative processing:
-Abstraction of execution details: Users describe the desired outcome, not the steps to achieve it.
-Automatic optimization: The system applies query planning and execution tuning.
-Reduced complexity: Removes the need for explicit control structures, improving maintainability.
-Related concepts: Declarative programming includes domain-specific and functional programming paradigms.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Use cases</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> for declarative processing:
-SQL-based transformations in batch and streaming workflows.
-High-level data processing frameworks such as Lakeflow Declarative Pipelines.
-Scalable, distributed data workloads requiring automated optimizations.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Lakeflow Declarative Pipelines is a declarative framework</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> designed to simplify the creation of reliable and maintainable stream processing pipelines. By specifying what data to ingest and how to transform it, Lakeflow Declarative Pipelines automates key aspects of pipeline management, including orchestration, compute management, monitoring, data quality enforcement, and error handling.</t>
-    </r>
   </si>
   <si>
     <t>Key differences: procedural vs. declarative processing</t>
@@ -1772,18 +1649,96 @@
   <si>
     <t>Enable Hierarchical namespace: yes</t>
   </si>
+  <si>
+    <r>
+      <t>Characteristics</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Bahnschrift"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> of procedural processing:
+Step-by-step execution: The developer explicitly defines the order of operations.
+Use of control structures: Loops, conditionals, and functions manage execution flow.
+Detailed resource control: Enables fine-grained optimizations and manual performance tuning.
+Related concepts: Procedural programming is a sub-class of imperative programming.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Use cases</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Bahnschrift"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> for procedural processing:
+Custom ETL pipelines requiring procedural logic.
+Low-level performance optimizations in batch and streaming workflows.
+Legacy systems or existing imperative scripts.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Characteristics</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Bahnschrift"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> of declarative processing:
+Abstraction of execution details: Users describe the desired outcome, not the steps to achieve it.
+Automatic optimization: The system applies query planning and execution tuning.
+Reduced complexity: Removes the need for explicit control structures, improving maintainability.
+Related concepts: Declarative programming includes domain-specific and functional programming paradigms.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Use cases</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Bahnschrift"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> for declarative processing:
+SQL-based transformations in batch and streaming workflows.
+High-level data processing frameworks such as Lakeflow Declarative Pipelines.
+Scalable, distributed data workloads requiring automated optimizations.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Lakeflow Declarative Pipelines is a declarative framework</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Bahnschrift"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> designed to simplify the creation of reliable and maintainable stream processing pipelines. By specifying what data to ingest and how to transform it, Lakeflow Declarative Pipelines automates key aspects of pipeline management, including orchestration, compute management, monitoring, data quality enforcement, and error handling.</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-  </numFmts>
-  <fonts count="29">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="11">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1843,352 +1798,28 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <name val="Bahnschrift"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <name val="Bahnschrift"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -2196,251 +1827,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -2451,24 +1840,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2488,7 +1859,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2511,69 +1881,42 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hyperlink" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
@@ -2589,13 +1932,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2" descr="A diagram of the lakehouse architecture using Unity Catalog and delta tables."/>
+        <xdr:cNvPr id="3" name="Picture 2" descr="A diagram of the lakehouse architecture using Unity Catalog and delta tables.">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1" r:link="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" r:link="rId2"/>
         <a:srcRect l="783" b="14452"/>
         <a:stretch>
           <a:fillRect/>
@@ -2632,13 +1981,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3"/>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId3" r:link="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" r:link="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2674,13 +2029,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4"/>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId4" r:link="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" r:link="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2716,13 +2077,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Picture 5"/>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId5" r:link="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" r:link="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2758,13 +2125,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6"/>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId6" r:link="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" r:link="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2789,7 +2162,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -2805,13 +2178,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2836,7 +2215,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -2852,13 +2231,19 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="Diagram: Databricks architecture"/>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Diagram: Databricks architecture">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1" r:link="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" r:link="rId2"/>
         <a:srcRect t="5907" r="5963" b="5887"/>
         <a:stretch>
           <a:fillRect/>
@@ -2884,7 +2269,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -2895,18 +2280,24 @@
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>6336665</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>130175</xdr:rowOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>27609</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1"/>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3202,24 +2593,24 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="B1:D190"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5" outlineLevelCol="3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D190"/>
+  <sheetFormatPr defaultColWidth="9.25" defaultRowHeight="15.5"/>
   <cols>
-    <col min="1" max="1" width="1.12307692307692" style="20" customWidth="1"/>
-    <col min="2" max="2" width="2.24615384615385" style="2" customWidth="1"/>
-    <col min="3" max="3" width="2.19230769230769" style="2" customWidth="1"/>
-    <col min="4" max="4" width="102.361538461538" style="21" customWidth="1"/>
-    <col min="5" max="16384" width="9.23076923076923" style="2"/>
+    <col min="1" max="1" width="1.08203125" style="13" customWidth="1"/>
+    <col min="2" max="2" width="2.25" style="2" customWidth="1"/>
+    <col min="3" max="3" width="2.1640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="102.33203125" style="14" customWidth="1"/>
+    <col min="5" max="16384" width="9.25" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="4:4">
-      <c r="D1" s="22" t="s">
+    <row r="1" spans="2:4">
+      <c r="D1" s="15" t="s">
         <v>0</v>
       </c>
     </row>
@@ -3227,1638 +2618,1634 @@
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="22"/>
-    </row>
-    <row r="3" ht="46.5" spans="2:4">
+      <c r="D2" s="15"/>
+    </row>
+    <row r="3" spans="2:4" ht="46.5">
       <c r="B3"/>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="14" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" ht="31" spans="4:4">
-      <c r="D5" s="21" t="s">
+    <row r="5" spans="2:4" ht="31">
+      <c r="D5" s="14" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" ht="31" spans="4:4">
-      <c r="D6" s="22" t="s">
+    <row r="6" spans="2:4" ht="46.5">
+      <c r="D6" s="15" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="4:4">
-      <c r="D7" s="22"/>
-    </row>
-    <row r="8" spans="4:4">
-      <c r="D8" s="22"/>
-    </row>
-    <row r="9" spans="3:3">
-      <c r="C9" s="13" t="s">
+    <row r="7" spans="2:4">
+      <c r="D7" s="15"/>
+    </row>
+    <row r="8" spans="2:4">
+      <c r="D8" s="15"/>
+    </row>
+    <row r="9" spans="2:4">
+      <c r="C9" s="7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="4:4">
-      <c r="D10" s="21" t="s">
+    <row r="10" spans="2:4">
+      <c r="D10" s="14" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="4:4">
-      <c r="D11" s="23" t="s">
+    <row r="11" spans="2:4">
+      <c r="D11" s="16" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="2:2">
+    <row r="13" spans="2:4" ht="16">
       <c r="B13"/>
     </row>
-    <row r="25" ht="108.5" spans="4:4">
-      <c r="D25" s="21" t="s">
+    <row r="25" spans="3:4" ht="108.5">
+      <c r="D25" s="14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="4:4">
-      <c r="D26" s="21" t="s">
+    <row r="26" spans="3:4">
+      <c r="D26" s="14" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="3:3">
-      <c r="C28" s="13" t="s">
+    <row r="28" spans="3:4">
+      <c r="C28" s="7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="29" ht="31" spans="4:4">
-      <c r="D29" s="21" t="s">
+    <row r="29" spans="3:4" ht="31">
+      <c r="D29" s="14" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="4:4">
-      <c r="D31" s="24" t="s">
+    <row r="31" spans="3:4">
+      <c r="D31" s="17" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="4:4">
-      <c r="D32" s="21" t="s">
+    <row r="32" spans="3:4">
+      <c r="D32" s="14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="4:4">
-      <c r="D33" s="21" t="s">
+    <row r="33" spans="2:4">
+      <c r="D33" s="14" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="35" ht="325.5" spans="4:4">
-      <c r="D35" s="22" t="s">
+    <row r="35" spans="2:4" ht="372">
+      <c r="D35" s="15" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="36" spans="2:4">
+    <row r="36" spans="2:4" ht="16">
       <c r="B36"/>
       <c r="C36"/>
-      <c r="D36" s="23"/>
-    </row>
-    <row r="37" spans="2:4">
+      <c r="D36" s="16"/>
+    </row>
+    <row r="37" spans="2:4" ht="16">
       <c r="B37"/>
       <c r="C37"/>
-      <c r="D37" s="23" t="s">
+      <c r="D37" s="16" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="38" spans="2:4">
+    <row r="38" spans="2:4" ht="16">
       <c r="B38"/>
       <c r="C38"/>
-      <c r="D38" s="23" t="s">
+      <c r="D38" s="16" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="2:4">
+    <row r="39" spans="2:4" ht="16">
       <c r="B39"/>
       <c r="C39"/>
-      <c r="D39" s="23"/>
-    </row>
-    <row r="40" spans="2:4">
+      <c r="D39" s="16"/>
+    </row>
+    <row r="40" spans="2:4" ht="16">
       <c r="B40"/>
       <c r="C40"/>
-      <c r="D40" s="23"/>
-    </row>
-    <row r="41" spans="2:3">
+      <c r="D40" s="16"/>
+    </row>
+    <row r="41" spans="2:4" ht="16">
       <c r="B41"/>
-      <c r="C41" s="25" t="s">
+      <c r="C41" s="18" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="42" spans="2:4">
+    <row r="42" spans="2:4" ht="16">
       <c r="B42"/>
       <c r="C42"/>
-      <c r="D42" s="23" t="s">
+      <c r="D42" s="16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="43" ht="17.5" spans="2:4">
+    <row r="43" spans="2:4" ht="17.5">
       <c r="B43"/>
       <c r="C43"/>
-      <c r="D43" s="26" t="s">
+      <c r="D43" s="19" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="2:4">
+    <row r="44" spans="2:4" ht="16">
       <c r="B44"/>
       <c r="C44"/>
-      <c r="D44" s="23" t="s">
+      <c r="D44" s="16" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="45" spans="2:4">
+    <row r="45" spans="2:4" ht="16">
       <c r="B45"/>
       <c r="C45"/>
-      <c r="D45" s="23" t="s">
+      <c r="D45" s="16" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="46" ht="77.5" spans="2:4">
+    <row r="46" spans="2:4" ht="93">
       <c r="B46"/>
       <c r="C46"/>
-      <c r="D46" s="21" t="s">
+      <c r="D46" s="14" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="47" spans="2:4">
+    <row r="47" spans="2:4" ht="16">
       <c r="B47"/>
       <c r="C47"/>
-      <c r="D47" s="23"/>
-    </row>
-    <row r="48" ht="139.5" spans="2:4">
+      <c r="D47" s="16"/>
+    </row>
+    <row r="48" spans="2:4" ht="139.5">
       <c r="B48"/>
       <c r="C48"/>
-      <c r="D48" s="22" t="s">
+      <c r="D48" s="15" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="2:4">
+    <row r="49" spans="2:4" ht="16">
       <c r="B49"/>
       <c r="C49"/>
-      <c r="D49" s="23"/>
-    </row>
-    <row r="50" ht="31" spans="2:4">
+      <c r="D49" s="16"/>
+    </row>
+    <row r="50" spans="2:4" ht="31">
       <c r="B50"/>
       <c r="C50"/>
-      <c r="D50" s="21" t="s">
+      <c r="D50" s="14" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="51" spans="2:4">
+    <row r="51" spans="2:4" ht="16">
       <c r="B51"/>
       <c r="C51"/>
-      <c r="D51" s="23"/>
-    </row>
-    <row r="52" spans="2:4">
+      <c r="D51" s="16"/>
+    </row>
+    <row r="52" spans="2:4" ht="16">
       <c r="B52"/>
       <c r="C52"/>
-      <c r="D52" s="23"/>
-    </row>
-    <row r="53" spans="2:4">
+      <c r="D52" s="16"/>
+    </row>
+    <row r="53" spans="2:4" ht="16">
       <c r="B53"/>
       <c r="C53"/>
-      <c r="D53" s="23" t="s">
+      <c r="D53" s="16" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="54" spans="2:4">
+    <row r="54" spans="2:4" ht="16">
       <c r="B54"/>
       <c r="C54"/>
-      <c r="D54" s="25" t="s">
+      <c r="D54" s="18" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="55" ht="62" spans="2:4">
+    <row r="55" spans="2:4" ht="62">
       <c r="B55"/>
       <c r="C55"/>
-      <c r="D55" s="21" t="s">
+      <c r="D55" s="14" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="2:4">
+    <row r="56" spans="2:4" ht="16">
       <c r="B56"/>
       <c r="C56"/>
-      <c r="D56" s="23"/>
-    </row>
-    <row r="57" ht="170.5" spans="2:4">
+      <c r="D56" s="16"/>
+    </row>
+    <row r="57" spans="2:4" ht="170.5">
       <c r="B57"/>
       <c r="C57"/>
-      <c r="D57" s="21" t="s">
+      <c r="D57" s="14" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="58" spans="2:4">
+    <row r="58" spans="2:4" ht="16">
       <c r="B58"/>
       <c r="C58"/>
-      <c r="D58" s="23"/>
-    </row>
-    <row r="59" spans="2:3">
+      <c r="D58" s="16"/>
+    </row>
+    <row r="59" spans="2:4" ht="16">
       <c r="B59"/>
-      <c r="C59" s="25" t="s">
+      <c r="C59" s="18" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="60" spans="2:4">
+    <row r="60" spans="2:4" ht="16">
       <c r="B60"/>
       <c r="C60"/>
-      <c r="D60" s="23" t="s">
+      <c r="D60" s="16" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="2:4">
+    <row r="61" spans="2:4" ht="16">
       <c r="B61"/>
       <c r="C61"/>
-      <c r="D61" s="23" t="s">
+      <c r="D61" s="16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="62" spans="2:4">
+    <row r="62" spans="2:4" ht="16">
       <c r="B62"/>
       <c r="C62"/>
-      <c r="D62" s="22" t="s">
+      <c r="D62" s="15" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="63" spans="2:4">
+    <row r="63" spans="2:4" ht="16">
       <c r="B63"/>
       <c r="C63"/>
-      <c r="D63" s="22" t="s">
+      <c r="D63" s="15" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="64" ht="18" customHeight="1" spans="2:4">
+    <row r="64" spans="2:4" ht="18" customHeight="1">
       <c r="B64"/>
       <c r="C64"/>
-      <c r="D64" s="22"/>
-    </row>
-    <row r="65" ht="156" customHeight="1" spans="2:4">
+      <c r="D64" s="15"/>
+    </row>
+    <row r="65" spans="2:4" ht="156" customHeight="1">
       <c r="B65"/>
       <c r="C65"/>
-      <c r="D65" s="22" t="s">
+      <c r="D65" s="15" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="66" spans="2:4">
+    <row r="66" spans="2:4" ht="16">
       <c r="B66"/>
       <c r="C66"/>
-      <c r="D66" s="23"/>
-    </row>
-    <row r="67" spans="2:4">
+      <c r="D66" s="16"/>
+    </row>
+    <row r="67" spans="2:4" ht="16">
       <c r="B67"/>
       <c r="C67"/>
-      <c r="D67" s="12"/>
-    </row>
-    <row r="68" spans="2:4">
+      <c r="D67" s="6"/>
+    </row>
+    <row r="68" spans="2:4" ht="16">
       <c r="B68"/>
       <c r="C68"/>
-      <c r="D68" s="23"/>
-    </row>
-    <row r="69" spans="2:4">
+      <c r="D68" s="16"/>
+    </row>
+    <row r="69" spans="2:4" ht="16">
       <c r="B69"/>
       <c r="C69"/>
-      <c r="D69" s="23"/>
-    </row>
-    <row r="70" spans="2:4">
+      <c r="D69" s="16"/>
+    </row>
+    <row r="70" spans="2:4" ht="16">
       <c r="B70"/>
       <c r="C70"/>
-      <c r="D70" s="23"/>
-    </row>
-    <row r="71" spans="2:4">
+      <c r="D70" s="16"/>
+    </row>
+    <row r="71" spans="2:4" ht="16">
       <c r="B71"/>
       <c r="C71"/>
-      <c r="D71" s="23"/>
-    </row>
-    <row r="72" spans="2:4">
+      <c r="D71" s="16"/>
+    </row>
+    <row r="72" spans="2:4" ht="16">
       <c r="B72"/>
       <c r="C72"/>
-      <c r="D72" s="23"/>
-    </row>
-    <row r="73" spans="2:4">
+      <c r="D72" s="16"/>
+    </row>
+    <row r="73" spans="2:4" ht="16">
       <c r="B73"/>
       <c r="C73"/>
-      <c r="D73" s="23"/>
-    </row>
-    <row r="74" spans="2:4">
+      <c r="D73" s="16"/>
+    </row>
+    <row r="74" spans="2:4" ht="16">
       <c r="B74"/>
       <c r="C74"/>
-      <c r="D74" s="23"/>
-    </row>
-    <row r="75" spans="2:4">
+      <c r="D74" s="16"/>
+    </row>
+    <row r="75" spans="2:4" ht="16">
       <c r="B75"/>
       <c r="C75"/>
-      <c r="D75" s="23"/>
-    </row>
-    <row r="76" spans="2:4">
+      <c r="D75" s="16"/>
+    </row>
+    <row r="76" spans="2:4" ht="16">
       <c r="B76"/>
       <c r="C76"/>
-      <c r="D76" s="23"/>
-    </row>
-    <row r="77" spans="2:4">
+      <c r="D76" s="16"/>
+    </row>
+    <row r="77" spans="2:4" ht="16">
       <c r="B77"/>
       <c r="C77"/>
-      <c r="D77" s="23"/>
-    </row>
-    <row r="78" spans="2:4">
+      <c r="D77" s="16"/>
+    </row>
+    <row r="78" spans="2:4" ht="16">
       <c r="B78"/>
       <c r="C78"/>
-      <c r="D78" s="23"/>
-    </row>
-    <row r="79" spans="2:4">
+      <c r="D78" s="16"/>
+    </row>
+    <row r="79" spans="2:4" ht="16">
       <c r="B79"/>
       <c r="C79"/>
-      <c r="D79" s="23"/>
-    </row>
-    <row r="84" spans="4:4">
-      <c r="D84" s="21" t="s">
+      <c r="D79" s="16"/>
+    </row>
+    <row r="84" spans="4:4" ht="31">
+      <c r="D84" s="14" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="86" spans="4:4">
-      <c r="D86" s="22" t="s">
+      <c r="D86" s="15" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="87" ht="31" spans="4:4">
-      <c r="D87" s="21" t="s">
+    <row r="87" spans="4:4" ht="31">
+      <c r="D87" s="14" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="89" ht="46.5" spans="4:4">
-      <c r="D89" s="21" t="s">
+    <row r="89" spans="4:4" ht="46.5">
+      <c r="D89" s="14" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="91" ht="31" spans="4:4">
-      <c r="D91" s="21" t="s">
+    <row r="91" spans="4:4" ht="31">
+      <c r="D91" s="14" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="93" ht="46.5" spans="4:4">
-      <c r="D93" s="21" t="s">
+    <row r="93" spans="4:4" ht="46.5">
+      <c r="D93" s="14" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="95" ht="31" spans="4:4">
-      <c r="D95" s="21" t="s">
+    <row r="95" spans="4:4" ht="46.5">
+      <c r="D95" s="14" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="97" spans="4:4">
-      <c r="D97" s="12"/>
+      <c r="D97" s="6"/>
     </row>
     <row r="116" spans="4:4">
-      <c r="D116" s="22" t="s">
+      <c r="D116" s="15" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="117" ht="31" spans="4:4">
-      <c r="D117" s="21" t="s">
+    <row r="117" spans="4:4" ht="46.5">
+      <c r="D117" s="14" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="119" ht="46.5" spans="4:4">
-      <c r="D119" s="21" t="s">
+    <row r="119" spans="4:4" ht="46.5">
+      <c r="D119" s="14" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="121" ht="46.5" spans="4:4">
-      <c r="D121" s="21" t="s">
+    <row r="121" spans="4:4" ht="46.5">
+      <c r="D121" s="14" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="123" ht="46.5" spans="4:4">
-      <c r="D123" s="21" t="s">
+    <row r="123" spans="4:4" ht="46.5">
+      <c r="D123" s="14" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="125" ht="62" spans="4:4">
-      <c r="D125" s="21" t="s">
+    <row r="125" spans="4:4" ht="62">
+      <c r="D125" s="14" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="127" ht="46.5" spans="4:4">
-      <c r="D127" s="21" t="s">
+    <row r="127" spans="4:4" ht="46.5">
+      <c r="D127" s="14" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="129" spans="2:2">
+    <row r="129" spans="2:2" ht="16">
       <c r="B129"/>
     </row>
-    <row r="145" spans="4:4">
-      <c r="D145" s="22" t="s">
+    <row r="145" spans="2:4" ht="31">
+      <c r="D145" s="15" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="146" ht="46.5" spans="4:4">
-      <c r="D146" s="21" t="s">
+    <row r="146" spans="2:4" ht="46.5">
+      <c r="D146" s="14" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="148" ht="46.5" spans="4:4">
-      <c r="D148" s="21" t="s">
+    <row r="148" spans="2:4" ht="46.5">
+      <c r="D148" s="14" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="150" ht="46.5" spans="4:4">
-      <c r="D150" s="21" t="s">
+    <row r="150" spans="2:4" ht="46.5">
+      <c r="D150" s="14" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="152" ht="46.5" spans="4:4">
-      <c r="D152" s="21" t="s">
+    <row r="152" spans="2:4" ht="46.5">
+      <c r="D152" s="14" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="154" spans="2:2">
+    <row r="154" spans="2:4" ht="16">
       <c r="B154"/>
     </row>
     <row r="173" spans="4:4">
-      <c r="D173" s="22" t="s">
+      <c r="D173" s="15" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="174" spans="4:4">
-      <c r="D174" s="21" t="s">
+      <c r="D174" s="14" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="176" ht="62" spans="4:4">
-      <c r="D176" s="27" t="s">
+    <row r="176" spans="4:4" ht="77.5">
+      <c r="D176" s="20" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="177" spans="4:4">
-      <c r="D177" s="12"/>
-    </row>
-    <row r="178" ht="46.5" spans="4:4">
-      <c r="D178" s="27" t="s">
+      <c r="D177" s="6"/>
+    </row>
+    <row r="178" spans="4:4" ht="62">
+      <c r="D178" s="20" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="179" spans="4:4">
-      <c r="D179" s="12"/>
-    </row>
-    <row r="180" ht="46.5" spans="4:4">
-      <c r="D180" s="27" t="s">
+      <c r="D179" s="6"/>
+    </row>
+    <row r="180" spans="4:4" ht="46.5">
+      <c r="D180" s="20" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="181" spans="4:4">
-      <c r="D181" s="12"/>
-    </row>
-    <row r="182" ht="62" spans="4:4">
-      <c r="D182" s="27" t="s">
+      <c r="D181" s="6"/>
+    </row>
+    <row r="182" spans="4:4" ht="77.5">
+      <c r="D182" s="20" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="183" spans="4:4">
-      <c r="D183" s="12"/>
-    </row>
-    <row r="184" ht="31" spans="4:4">
-      <c r="D184" s="27" t="s">
+      <c r="D183" s="6"/>
+    </row>
+    <row r="184" spans="4:4" ht="31">
+      <c r="D184" s="20" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="185" spans="4:4">
-      <c r="D185" s="12"/>
-    </row>
-    <row r="186" ht="93" spans="4:4">
-      <c r="D186" s="27" t="s">
+      <c r="D185" s="6"/>
+    </row>
+    <row r="186" spans="4:4" ht="108.5">
+      <c r="D186" s="20" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="188" spans="4:4">
-      <c r="D188" s="22" t="s">
+      <c r="D188" s="15" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="189" ht="31" spans="4:4">
-      <c r="D189" s="21" t="s">
+    <row r="189" spans="4:4" ht="31">
+      <c r="D189" s="14" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="190" ht="46.5" spans="4:4">
-      <c r="D190" s="21" t="s">
+    <row r="190" spans="4:4" ht="62">
+      <c r="D190" s="14" t="s">
         <v>65</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D43" r:id="rId2" display="Delta refers to technologies related to or in the Delta Lake open source project" tooltip="https://delta.io/"/>
+    <hyperlink ref="D43" r:id="rId1" tooltip="https://delta.io/" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="1" orientation="portrait"/>
-  <headerFooter/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D192"/>
-  <sheetFormatPr defaultColWidth="8.66923076923077" defaultRowHeight="15.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15.5"/>
   <cols>
-    <col min="1" max="1" width="3" style="12" customWidth="1"/>
-    <col min="2" max="3" width="3.38461538461538" style="12" customWidth="1"/>
-    <col min="4" max="4" width="108.169230769231" style="15" customWidth="1"/>
-    <col min="5" max="16384" width="8.66923076923077" style="12"/>
+    <col min="1" max="1" width="3" style="6" customWidth="1"/>
+    <col min="2" max="3" width="3.4140625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="108.1640625" style="9" customWidth="1"/>
+    <col min="5" max="16384" width="8.6640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="5" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="3:3">
-      <c r="C2" s="12" t="s">
+    <row r="2" spans="1:4">
+      <c r="C2" s="6" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="2:2">
-      <c r="B4" s="12" t="s">
+    <row r="4" spans="1:4">
+      <c r="B4" s="6" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="2:2">
-      <c r="B5" s="12" t="s">
+    <row r="5" spans="1:4">
+      <c r="B5" s="6" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="2:2">
-      <c r="B6" s="12" t="s">
+    <row r="6" spans="1:4">
+      <c r="B6" s="6" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="2:2">
-      <c r="B7" s="11" t="s">
+    <row r="7" spans="1:4">
+      <c r="B7" s="5" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="8" hidden="1" spans="3:3">
-      <c r="C8" s="12" t="s">
+    <row r="8" spans="1:4" hidden="1">
+      <c r="C8" s="6" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="9" hidden="1" spans="4:4">
-      <c r="D9" s="15" t="s">
+    <row r="9" spans="1:4" ht="31" hidden="1">
+      <c r="D9" s="9" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="10" hidden="1" spans="3:3">
-      <c r="C10" s="12" t="s">
+    <row r="10" spans="1:4" hidden="1">
+      <c r="C10" s="6" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="11" hidden="1" spans="4:4">
-      <c r="D11" s="15" t="s">
+    <row r="11" spans="1:4" hidden="1">
+      <c r="D11" s="9" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="12" hidden="1" spans="4:4">
-      <c r="D12" s="15" t="s">
+    <row r="12" spans="1:4" hidden="1">
+      <c r="D12" s="9" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="13" hidden="1" spans="4:4">
-      <c r="D13" s="15" t="s">
+    <row r="13" spans="1:4" hidden="1">
+      <c r="D13" s="9" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="14" hidden="1" spans="4:4">
-      <c r="D14" s="16" t="s">
+    <row r="14" spans="1:4" hidden="1">
+      <c r="D14" s="10" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="15" hidden="1" spans="3:3">
-      <c r="C15" s="12" t="s">
+    <row r="15" spans="1:4" hidden="1">
+      <c r="C15" s="6" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="16" hidden="1" spans="4:4">
-      <c r="D16" s="15" t="s">
+    <row r="16" spans="1:4" hidden="1">
+      <c r="D16" s="9" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="17" hidden="1" spans="4:4">
-      <c r="D17" s="15" t="s">
+    <row r="17" spans="2:4" hidden="1">
+      <c r="D17" s="9" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="19" spans="2:2">
-      <c r="B19" s="11" t="s">
+    <row r="19" spans="2:4">
+      <c r="B19" s="5" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="4:4">
-      <c r="D20" s="15" t="s">
+    <row r="20" spans="2:4">
+      <c r="D20" s="9" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="4:4">
-      <c r="D21" s="15" t="s">
+    <row r="21" spans="2:4">
+      <c r="D21" s="9" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="31" spans="3:3">
-      <c r="C31" s="11" t="s">
+    <row r="31" spans="2:4">
+      <c r="C31" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="32" ht="31" spans="3:4">
-      <c r="C32" s="11"/>
-      <c r="D32" s="15" t="s">
+    <row r="32" spans="2:4" ht="31">
+      <c r="C32" s="5"/>
+      <c r="D32" s="9" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="33" hidden="1" spans="3:4">
-      <c r="C33" s="11"/>
-      <c r="D33" s="15" t="s">
+    <row r="33" spans="3:4" hidden="1">
+      <c r="C33" s="5"/>
+      <c r="D33" s="9" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="34" hidden="1" spans="3:4">
-      <c r="C34" s="11"/>
-      <c r="D34" s="15" t="s">
+    <row r="34" spans="3:4" hidden="1">
+      <c r="C34" s="5"/>
+      <c r="D34" s="9" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="35" hidden="1" spans="3:4">
-      <c r="C35" s="11"/>
-      <c r="D35" s="15" t="s">
+    <row r="35" spans="3:4" hidden="1">
+      <c r="C35" s="5"/>
+      <c r="D35" s="9" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="36" hidden="1" spans="3:4">
-      <c r="C36" s="11"/>
-      <c r="D36" s="15" t="s">
+    <row r="36" spans="3:4" hidden="1">
+      <c r="C36" s="5"/>
+      <c r="D36" s="9" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="37" hidden="1" spans="3:4">
-      <c r="C37" s="11"/>
-      <c r="D37" s="15" t="s">
+    <row r="37" spans="3:4" hidden="1">
+      <c r="C37" s="5"/>
+      <c r="D37" s="9" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="38" hidden="1" spans="3:4">
-      <c r="C38" s="11"/>
-      <c r="D38" s="15" t="s">
+    <row r="38" spans="3:4" hidden="1">
+      <c r="C38" s="5"/>
+      <c r="D38" s="9" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="39" ht="31" hidden="1" spans="3:4">
-      <c r="C39" s="11"/>
-      <c r="D39" s="15" t="s">
+    <row r="39" spans="3:4" ht="31" hidden="1">
+      <c r="C39" s="5"/>
+      <c r="D39" s="9" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="40" hidden="1" spans="3:3">
-      <c r="C40" s="11"/>
-    </row>
-    <row r="41" hidden="1" spans="3:3">
-      <c r="C41" s="11" t="s">
+    <row r="40" spans="3:4" hidden="1">
+      <c r="C40" s="5"/>
+    </row>
+    <row r="41" spans="3:4" hidden="1">
+      <c r="C41" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="42" ht="14" hidden="1" customHeight="1" spans="3:4">
-      <c r="C42" s="11"/>
-      <c r="D42" s="15" t="s">
+    <row r="42" spans="3:4" ht="14" hidden="1" customHeight="1">
+      <c r="C42" s="5"/>
+      <c r="D42" s="9" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="43" hidden="1" spans="3:4">
-      <c r="C43" s="11"/>
-      <c r="D43" s="15" t="s">
+    <row r="43" spans="3:4" hidden="1">
+      <c r="C43" s="5"/>
+      <c r="D43" s="9" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="44" hidden="1" spans="3:4">
-      <c r="C44" s="11"/>
-      <c r="D44" s="15" t="s">
+    <row r="44" spans="3:4" hidden="1">
+      <c r="C44" s="5"/>
+      <c r="D44" s="9" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="45" hidden="1" spans="3:4">
-      <c r="C45" s="11"/>
-      <c r="D45" s="15" t="s">
+    <row r="45" spans="3:4" hidden="1">
+      <c r="C45" s="5"/>
+      <c r="D45" s="9" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="46" hidden="1" spans="3:3">
-      <c r="C46" s="11" t="s">
+    <row r="46" spans="3:4" hidden="1">
+      <c r="C46" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="47" ht="31" hidden="1" spans="3:4">
-      <c r="C47" s="11"/>
-      <c r="D47" s="15" t="s">
+    <row r="47" spans="3:4" ht="31" hidden="1">
+      <c r="C47" s="5"/>
+      <c r="D47" s="9" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="48" hidden="1" spans="3:4">
-      <c r="C48" s="11"/>
-      <c r="D48" s="15" t="s">
+    <row r="48" spans="3:4" hidden="1">
+      <c r="C48" s="5"/>
+      <c r="D48" s="9" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="49" hidden="1" spans="3:3">
-      <c r="C49" s="11" t="s">
+    <row r="49" spans="3:4" hidden="1">
+      <c r="C49" s="5" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="50" ht="31" hidden="1" spans="3:4">
-      <c r="C50" s="11"/>
-      <c r="D50" s="15" t="s">
+    <row r="50" spans="3:4" ht="31" hidden="1">
+      <c r="C50" s="5"/>
+      <c r="D50" s="9" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="51" hidden="1" spans="3:4">
-      <c r="C51" s="11"/>
-      <c r="D51" s="15" t="s">
+    <row r="51" spans="3:4" hidden="1">
+      <c r="C51" s="5"/>
+      <c r="D51" s="9" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="52" hidden="1" spans="3:3">
-      <c r="C52" s="11" t="s">
+    <row r="52" spans="3:4" hidden="1">
+      <c r="C52" s="5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="53" hidden="1" spans="3:4">
-      <c r="C53" s="11"/>
-      <c r="D53" s="15" t="s">
+    <row r="53" spans="3:4" hidden="1">
+      <c r="C53" s="5"/>
+      <c r="D53" s="9" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="54" hidden="1" spans="3:4">
-      <c r="C54" s="11"/>
-      <c r="D54" s="15" t="s">
+    <row r="54" spans="3:4" hidden="1">
+      <c r="C54" s="5"/>
+      <c r="D54" s="9" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="55" hidden="1" spans="3:3">
-      <c r="C55" s="11" t="s">
+    <row r="55" spans="3:4" hidden="1">
+      <c r="C55" s="5" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="56" hidden="1" spans="3:4">
-      <c r="C56" s="11"/>
-      <c r="D56" s="15" t="s">
+    <row r="56" spans="3:4" hidden="1">
+      <c r="C56" s="5"/>
+      <c r="D56" s="9" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="57" hidden="1" spans="3:3">
-      <c r="C57" s="11" t="s">
+    <row r="57" spans="3:4" hidden="1">
+      <c r="C57" s="5" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="58" ht="31" hidden="1" spans="3:4">
-      <c r="C58" s="11"/>
-      <c r="D58" s="15" t="s">
+    <row r="58" spans="3:4" ht="31" hidden="1">
+      <c r="C58" s="5"/>
+      <c r="D58" s="9" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="59" hidden="1" spans="3:4">
-      <c r="C59" s="11"/>
-      <c r="D59" s="15" t="s">
+    <row r="59" spans="3:4" hidden="1">
+      <c r="C59" s="5"/>
+      <c r="D59" s="9" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="60" hidden="1" spans="3:3">
-      <c r="C60" s="11" t="s">
+    <row r="60" spans="3:4" hidden="1">
+      <c r="C60" s="5" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="61" ht="46.5" hidden="1" spans="3:4">
-      <c r="C61" s="11"/>
-      <c r="D61" s="15" t="s">
+    <row r="61" spans="3:4" ht="46.5" hidden="1">
+      <c r="C61" s="5"/>
+      <c r="D61" s="9" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="62" hidden="1" spans="3:4">
-      <c r="C62" s="11"/>
-      <c r="D62" s="15" t="s">
+    <row r="62" spans="3:4" hidden="1">
+      <c r="C62" s="5"/>
+      <c r="D62" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="63" hidden="1" spans="3:4">
-      <c r="C63" s="11"/>
-      <c r="D63" s="15" t="s">
+    <row r="63" spans="3:4" hidden="1">
+      <c r="C63" s="5"/>
+      <c r="D63" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="64" hidden="1" spans="3:3">
-      <c r="C64" s="11" t="s">
+    <row r="64" spans="3:4" hidden="1">
+      <c r="C64" s="5" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="65" ht="46.5" hidden="1" spans="3:4">
-      <c r="C65" s="11"/>
-      <c r="D65" s="15" t="s">
+    <row r="65" spans="2:4" ht="46.5" hidden="1">
+      <c r="C65" s="5"/>
+      <c r="D65" s="9" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="66" hidden="1" spans="3:4">
-      <c r="C66" s="11"/>
-      <c r="D66" s="15" t="s">
+    <row r="66" spans="2:4" hidden="1">
+      <c r="C66" s="5"/>
+      <c r="D66" s="9" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="67" hidden="1" spans="3:3">
-      <c r="C67" s="11" t="s">
+    <row r="67" spans="2:4" hidden="1">
+      <c r="C67" s="5" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="68" ht="31" hidden="1" spans="3:4">
-      <c r="C68" s="11"/>
-      <c r="D68" s="15" t="s">
+    <row r="68" spans="2:4" ht="31" hidden="1">
+      <c r="C68" s="5"/>
+      <c r="D68" s="9" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="69" hidden="1" spans="4:4">
-      <c r="D69" s="15" t="s">
+    <row r="69" spans="2:4" hidden="1">
+      <c r="D69" s="9" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="70" hidden="1" spans="4:4">
-      <c r="D70" s="15" t="s">
+    <row r="70" spans="2:4" hidden="1">
+      <c r="D70" s="9" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="72" spans="2:2">
-      <c r="B72" s="11" t="s">
+    <row r="72" spans="2:4">
+      <c r="B72" s="5" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="73" spans="3:3">
-      <c r="C73" s="12" t="s">
+    <row r="73" spans="2:4">
+      <c r="C73" s="6" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="74" hidden="1" spans="4:4">
-      <c r="D74" s="15" t="s">
+    <row r="74" spans="2:4" ht="31" hidden="1">
+      <c r="D74" s="9" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="75" hidden="1" spans="3:4">
-      <c r="C75" s="17"/>
-      <c r="D75" s="15" t="s">
+    <row r="75" spans="2:4" hidden="1">
+      <c r="C75" s="11"/>
+      <c r="D75" s="9" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="76" ht="31" hidden="1" spans="3:4">
-      <c r="C76" s="17" t="s">
+    <row r="76" spans="2:4" ht="31" hidden="1">
+      <c r="C76" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="D76" s="15" t="s">
+      <c r="D76" s="9" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="77" ht="31" hidden="1" spans="3:4">
-      <c r="C77" s="17" t="s">
+    <row r="77" spans="2:4" ht="31" hidden="1">
+      <c r="C77" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="D77" s="15" t="s">
+      <c r="D77" s="9" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="78" hidden="1" spans="3:3">
-      <c r="C78" s="17" t="s">
+    <row r="78" spans="2:4" hidden="1">
+      <c r="C78" s="11" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="79" ht="31" hidden="1" spans="3:4">
-      <c r="C79" s="17"/>
-      <c r="D79" s="15" t="s">
+    <row r="79" spans="2:4" ht="31" hidden="1">
+      <c r="C79" s="11"/>
+      <c r="D79" s="9" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="80" hidden="1" spans="3:4">
-      <c r="C80" s="17"/>
-      <c r="D80" s="15" t="s">
+    <row r="80" spans="2:4" hidden="1">
+      <c r="C80" s="11"/>
+      <c r="D80" s="9" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="81" ht="33" hidden="1" customHeight="1" spans="3:4">
-      <c r="C81" s="17"/>
-      <c r="D81" s="15" t="s">
+    <row r="81" spans="3:4" ht="33" hidden="1" customHeight="1">
+      <c r="C81" s="11"/>
+      <c r="D81" s="9" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="82" hidden="1" spans="3:3">
-      <c r="C82" s="17" t="s">
+    <row r="82" spans="3:4" hidden="1">
+      <c r="C82" s="11" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="83" hidden="1" spans="3:4">
-      <c r="C83" s="17"/>
-      <c r="D83" s="15" t="s">
+    <row r="83" spans="3:4" ht="31" hidden="1">
+      <c r="C83" s="11"/>
+      <c r="D83" s="9" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="84" ht="31" hidden="1" spans="3:4">
-      <c r="C84" s="17"/>
-      <c r="D84" s="15" t="s">
+    <row r="84" spans="3:4" ht="31" hidden="1">
+      <c r="C84" s="11"/>
+      <c r="D84" s="9" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="85" ht="46.5" hidden="1" spans="3:4">
-      <c r="C85" s="17"/>
-      <c r="D85" s="15" t="s">
+    <row r="85" spans="3:4" ht="46.5" hidden="1">
+      <c r="C85" s="11"/>
+      <c r="D85" s="9" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="86" hidden="1" spans="3:3">
-      <c r="C86" s="17" t="s">
+    <row r="86" spans="3:4" hidden="1">
+      <c r="C86" s="11" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="87" ht="31" hidden="1" spans="3:4">
-      <c r="C87" s="17"/>
-      <c r="D87" s="15" t="s">
+    <row r="87" spans="3:4" ht="31" hidden="1">
+      <c r="C87" s="11"/>
+      <c r="D87" s="9" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="88" hidden="1" spans="3:4">
-      <c r="C88" s="17"/>
-      <c r="D88" s="15" t="s">
+    <row r="88" spans="3:4" hidden="1">
+      <c r="C88" s="11"/>
+      <c r="D88" s="9" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="89" hidden="1" spans="3:4">
-      <c r="C89" s="17"/>
-      <c r="D89" s="15" t="s">
+    <row r="89" spans="3:4" hidden="1">
+      <c r="C89" s="11"/>
+      <c r="D89" s="9" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="90" hidden="1" spans="3:4">
-      <c r="C90" s="17"/>
-      <c r="D90" s="15" t="s">
+    <row r="90" spans="3:4" hidden="1">
+      <c r="C90" s="11"/>
+      <c r="D90" s="9" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="91" hidden="1" spans="3:4">
-      <c r="C91" s="17"/>
-      <c r="D91" s="15" t="s">
+    <row r="91" spans="3:4" hidden="1">
+      <c r="C91" s="11"/>
+      <c r="D91" s="9" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="92" hidden="1" spans="3:4">
-      <c r="C92" s="17"/>
-      <c r="D92" s="15" t="s">
+    <row r="92" spans="3:4" ht="31" hidden="1">
+      <c r="C92" s="11"/>
+      <c r="D92" s="9" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="93" hidden="1" spans="3:4">
-      <c r="C93" s="17"/>
-      <c r="D93" s="15" t="s">
+    <row r="93" spans="3:4" hidden="1">
+      <c r="C93" s="11"/>
+      <c r="D93" s="9" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="94" hidden="1" spans="3:3">
-      <c r="C94" s="17" t="s">
+    <row r="94" spans="3:4" hidden="1">
+      <c r="C94" s="11" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="95" ht="31" hidden="1" spans="3:4">
-      <c r="C95" s="17"/>
-      <c r="D95" s="15" t="s">
+    <row r="95" spans="3:4" ht="31" hidden="1">
+      <c r="C95" s="11"/>
+      <c r="D95" s="9" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="96" hidden="1" spans="4:4">
-      <c r="D96" s="15" t="s">
+    <row r="96" spans="3:4" ht="31" hidden="1">
+      <c r="D96" s="9" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="97" ht="31" hidden="1" spans="4:4">
-      <c r="D97" s="15" t="s">
+    <row r="97" spans="2:4" ht="31" hidden="1">
+      <c r="D97" s="9" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="98" hidden="1" spans="3:3">
-      <c r="C98" s="12" t="s">
+    <row r="98" spans="2:4" hidden="1">
+      <c r="C98" s="6" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="99" ht="31" hidden="1" spans="4:4">
-      <c r="D99" s="15" t="s">
+    <row r="99" spans="2:4" ht="31" hidden="1">
+      <c r="D99" s="9" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="101" spans="2:2">
-      <c r="B101" s="11" t="s">
+    <row r="101" spans="2:4">
+      <c r="B101" s="5" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="102" spans="4:4">
-      <c r="D102" s="15" t="s">
+    <row r="102" spans="2:4">
+      <c r="D102" s="9" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="103" hidden="1" spans="3:3">
-      <c r="C103" s="12" t="s">
+    <row r="103" spans="2:4" hidden="1">
+      <c r="C103" s="6" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="104" ht="31" hidden="1" spans="4:4">
-      <c r="D104" s="15" t="s">
+    <row r="104" spans="2:4" ht="31" hidden="1">
+      <c r="D104" s="9" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="105" hidden="1" spans="3:3">
-      <c r="C105" s="12" t="s">
+    <row r="105" spans="2:4" hidden="1">
+      <c r="C105" s="6" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="106" ht="31" hidden="1" spans="4:4">
-      <c r="D106" s="15" t="s">
+    <row r="106" spans="2:4" ht="31" hidden="1">
+      <c r="D106" s="9" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="107" hidden="1" spans="4:4">
-      <c r="D107" s="15" t="s">
+    <row r="107" spans="2:4" hidden="1">
+      <c r="D107" s="9" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="108" hidden="1" spans="3:3">
-      <c r="C108" s="12" t="s">
+    <row r="108" spans="2:4" hidden="1">
+      <c r="C108" s="6" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="109" ht="31" hidden="1" spans="4:4">
-      <c r="D109" s="15" t="s">
+    <row r="109" spans="2:4" ht="31" hidden="1">
+      <c r="D109" s="9" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="110" hidden="1" spans="4:4">
-      <c r="D110" s="15" t="s">
+    <row r="110" spans="2:4" hidden="1">
+      <c r="D110" s="9" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="111" hidden="1" spans="3:3">
-      <c r="C111" s="12" t="s">
+    <row r="111" spans="2:4" hidden="1">
+      <c r="C111" s="6" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="112" ht="31" hidden="1" spans="4:4">
-      <c r="D112" s="15" t="s">
+    <row r="112" spans="2:4" ht="31" hidden="1">
+      <c r="D112" s="9" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="113" hidden="1" spans="4:4">
-      <c r="D113" s="15" t="s">
+    <row r="113" spans="2:4" hidden="1">
+      <c r="D113" s="9" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="115" spans="2:2">
-      <c r="B115" s="11" t="s">
+    <row r="115" spans="2:4">
+      <c r="B115" s="5" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="116" ht="31" spans="4:4">
-      <c r="D116" s="15" t="s">
+    <row r="116" spans="2:4" ht="31">
+      <c r="D116" s="9" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="117" hidden="1" spans="3:3">
-      <c r="C117" s="12" t="s">
+    <row r="117" spans="2:4" hidden="1">
+      <c r="C117" s="6" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="118" ht="31" hidden="1" spans="4:4">
-      <c r="D118" s="15" t="s">
+    <row r="118" spans="2:4" ht="31" hidden="1">
+      <c r="D118" s="9" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="119" hidden="1" spans="4:4">
-      <c r="D119" s="15" t="s">
+    <row r="119" spans="2:4" hidden="1">
+      <c r="D119" s="9" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="120" hidden="1" spans="3:3">
-      <c r="C120" s="12" t="s">
+    <row r="120" spans="2:4" hidden="1">
+      <c r="C120" s="6" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="121" ht="62" hidden="1" spans="4:4">
-      <c r="D121" s="15" t="s">
+    <row r="121" spans="2:4" ht="62" hidden="1">
+      <c r="D121" s="9" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="122" hidden="1" spans="4:4">
-      <c r="D122" s="15" t="s">
+    <row r="122" spans="2:4" hidden="1">
+      <c r="D122" s="9" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="123" hidden="1" spans="3:3">
-      <c r="C123" s="12" t="s">
+    <row r="123" spans="2:4" hidden="1">
+      <c r="C123" s="6" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="124" hidden="1" spans="4:4">
-      <c r="D124" s="15" t="s">
+    <row r="124" spans="2:4" hidden="1">
+      <c r="D124" s="9" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="125" hidden="1" spans="4:4">
-      <c r="D125" s="15" t="s">
+    <row r="125" spans="2:4" hidden="1">
+      <c r="D125" s="9" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="126" hidden="1" spans="4:4">
-      <c r="D126" s="15" t="s">
+    <row r="126" spans="2:4" hidden="1">
+      <c r="D126" s="9" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="127" hidden="1" spans="4:4">
-      <c r="D127" s="15" t="s">
+    <row r="127" spans="2:4" hidden="1">
+      <c r="D127" s="9" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="128" ht="31" hidden="1" spans="4:4">
-      <c r="D128" s="18" t="s">
+    <row r="128" spans="2:4" ht="31" hidden="1">
+      <c r="D128" s="12" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="129" hidden="1" spans="4:4">
-      <c r="D129" s="18" t="s">
+    <row r="129" spans="3:4" hidden="1">
+      <c r="D129" s="12" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="130" hidden="1" spans="4:4">
-      <c r="D130" s="18" t="s">
+    <row r="130" spans="3:4" ht="31" hidden="1">
+      <c r="D130" s="12" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="131" hidden="1" spans="4:4">
-      <c r="D131" s="18" t="s">
+    <row r="131" spans="3:4" hidden="1">
+      <c r="D131" s="12" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="132" hidden="1" spans="4:4">
-      <c r="D132" s="18" t="s">
+    <row r="132" spans="3:4" hidden="1">
+      <c r="D132" s="12" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="133" hidden="1" spans="3:3">
-      <c r="C133" s="12" t="s">
+    <row r="133" spans="3:4" hidden="1">
+      <c r="C133" s="6" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="134" ht="31" hidden="1" spans="4:4">
-      <c r="D134" s="15" t="s">
+    <row r="134" spans="3:4" ht="31" hidden="1">
+      <c r="D134" s="9" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="135" hidden="1" spans="4:4">
-      <c r="D135" s="15" t="s">
+    <row r="135" spans="3:4" hidden="1">
+      <c r="D135" s="9" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="136" ht="31" hidden="1" spans="4:4">
-      <c r="D136" s="15" t="s">
+    <row r="136" spans="3:4" ht="46.5" hidden="1">
+      <c r="D136" s="9" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="137" hidden="1" spans="3:3">
-      <c r="C137" s="12" t="s">
+    <row r="137" spans="3:4" hidden="1">
+      <c r="C137" s="6" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="138" hidden="1" spans="4:4">
-      <c r="D138" s="15" t="s">
+    <row r="138" spans="3:4" hidden="1">
+      <c r="D138" s="9" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="139" ht="31" hidden="1" spans="4:4">
-      <c r="D139" s="15" t="s">
+    <row r="139" spans="3:4" ht="31" hidden="1">
+      <c r="D139" s="9" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="140" hidden="1" spans="4:4">
-      <c r="D140" s="15" t="s">
+    <row r="140" spans="3:4" hidden="1">
+      <c r="D140" s="9" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="141" hidden="1" spans="4:4">
-      <c r="D141" s="15" t="s">
+    <row r="141" spans="3:4" hidden="1">
+      <c r="D141" s="9" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="142" hidden="1" spans="4:4">
-      <c r="D142" s="15" t="s">
+    <row r="142" spans="3:4" hidden="1">
+      <c r="D142" s="9" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="143" hidden="1" spans="4:4">
-      <c r="D143" s="15" t="s">
+    <row r="143" spans="3:4" hidden="1">
+      <c r="D143" s="9" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="144" ht="31" hidden="1" spans="4:4">
-      <c r="D144" s="15" t="s">
+    <row r="144" spans="3:4" ht="31" hidden="1">
+      <c r="D144" s="9" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="145" hidden="1" spans="3:3">
-      <c r="C145" s="12" t="s">
+    <row r="145" spans="2:4" hidden="1">
+      <c r="C145" s="6" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="146" ht="31" hidden="1" spans="4:4">
-      <c r="D146" s="15" t="s">
+    <row r="146" spans="2:4" ht="31" hidden="1">
+      <c r="D146" s="9" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="147" hidden="1" spans="4:4">
-      <c r="D147" s="15" t="s">
+    <row r="147" spans="2:4" hidden="1">
+      <c r="D147" s="9" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="148" hidden="1" spans="3:3">
-      <c r="C148" s="12" t="s">
+    <row r="148" spans="2:4" hidden="1">
+      <c r="C148" s="6" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="149" ht="46.5" hidden="1" spans="4:4">
-      <c r="D149" s="15" t="s">
+    <row r="149" spans="2:4" ht="46.5" hidden="1">
+      <c r="D149" s="9" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="150" hidden="1" spans="4:4">
-      <c r="D150" s="15" t="s">
+    <row r="150" spans="2:4" hidden="1">
+      <c r="D150" s="9" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="152" spans="2:2">
-      <c r="B152" s="11" t="s">
+    <row r="152" spans="2:4">
+      <c r="B152" s="5" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="153" ht="31" spans="4:4">
-      <c r="D153" s="15" t="s">
+    <row r="153" spans="2:4" ht="46.5">
+      <c r="D153" s="9" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="154" spans="4:4">
-      <c r="D154" s="15" t="s">
+    <row r="154" spans="2:4">
+      <c r="D154" s="9" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="155" hidden="1" spans="3:3">
-      <c r="C155" s="12" t="s">
+    <row r="155" spans="2:4" hidden="1">
+      <c r="C155" s="6" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="156" ht="31" hidden="1" spans="4:4">
-      <c r="D156" s="15" t="s">
+    <row r="156" spans="2:4" ht="31" hidden="1">
+      <c r="D156" s="9" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="157" hidden="1" spans="4:4">
-      <c r="D157" s="15" t="s">
+    <row r="157" spans="2:4" hidden="1">
+      <c r="D157" s="9" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="158" hidden="1" spans="3:3">
-      <c r="C158" s="12" t="s">
+    <row r="158" spans="2:4" hidden="1">
+      <c r="C158" s="6" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="159" ht="31" hidden="1" spans="4:4">
-      <c r="D159" s="15" t="s">
+    <row r="159" spans="2:4" ht="31" hidden="1">
+      <c r="D159" s="9" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="160" hidden="1" spans="4:4">
-      <c r="D160" s="15" t="s">
+    <row r="160" spans="2:4" hidden="1">
+      <c r="D160" s="9" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="161" hidden="1" spans="3:3">
-      <c r="C161" s="12" t="s">
+    <row r="161" spans="1:4" hidden="1">
+      <c r="C161" s="6" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="162" hidden="1" spans="4:4">
-      <c r="D162" s="15" t="s">
+    <row r="162" spans="1:4" hidden="1">
+      <c r="D162" s="9" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="163" hidden="1" spans="4:4">
-      <c r="D163" s="15" t="s">
+    <row r="163" spans="1:4" hidden="1">
+      <c r="D163" s="9" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="164" hidden="1" spans="3:3">
-      <c r="C164" s="12" t="s">
+    <row r="164" spans="1:4" hidden="1">
+      <c r="C164" s="6" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="165" ht="31" hidden="1" spans="4:4">
-      <c r="D165" s="15" t="s">
+    <row r="165" spans="1:4" ht="31" hidden="1">
+      <c r="D165" s="9" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="166" hidden="1" spans="4:4">
-      <c r="D166" s="15" t="s">
+    <row r="166" spans="1:4" hidden="1">
+      <c r="D166" s="9" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="167" hidden="1" spans="4:4">
-      <c r="D167" s="15" t="s">
+    <row r="167" spans="1:4" hidden="1">
+      <c r="D167" s="9" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="169" spans="1:1">
-      <c r="A169" s="19" t="s">
+    <row r="169" spans="1:4">
+      <c r="A169" s="5" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="170" spans="1:1">
-      <c r="A170" s="12" t="s">
+    <row r="170" spans="1:4">
+      <c r="A170" s="6" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="171" spans="2:2">
-      <c r="B171" s="12" t="s">
+    <row r="171" spans="1:4">
+      <c r="B171" s="6" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="172" spans="2:2">
-      <c r="B172" s="11" t="s">
+    <row r="172" spans="1:4">
+      <c r="B172" s="5" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="173" hidden="1" spans="3:3">
-      <c r="C173" s="12" t="s">
+    <row r="173" spans="1:4" hidden="1">
+      <c r="C173" s="6" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="174" hidden="1" spans="3:3">
-      <c r="C174" s="12" t="s">
+    <row r="174" spans="1:4" hidden="1">
+      <c r="C174" s="6" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="175" hidden="1" spans="3:3">
-      <c r="C175" s="12" t="s">
+    <row r="175" spans="1:4" hidden="1">
+      <c r="C175" s="6" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="176" hidden="1" spans="3:3">
-      <c r="C176" s="12" t="s">
+    <row r="176" spans="1:4" hidden="1">
+      <c r="C176" s="6" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="177" hidden="1" spans="3:3">
-      <c r="C177" s="12" t="s">
+    <row r="177" spans="1:4" hidden="1">
+      <c r="C177" s="6" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="178" ht="31" hidden="1" spans="4:4">
-      <c r="D178" s="15" t="s">
+    <row r="178" spans="1:4" ht="31" hidden="1">
+      <c r="D178" s="9" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="179" hidden="1" spans="3:3">
-      <c r="C179" s="12" t="s">
+    <row r="179" spans="1:4" hidden="1">
+      <c r="C179" s="6" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="180" hidden="1"/>
-    <row r="181" hidden="1" spans="3:3">
-      <c r="C181" s="12" t="s">
+    <row r="180" spans="1:4" hidden="1"/>
+    <row r="181" spans="1:4" hidden="1">
+      <c r="C181" s="6" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="182" hidden="1" spans="3:3">
-      <c r="C182" s="12" t="s">
+    <row r="182" spans="1:4" hidden="1">
+      <c r="C182" s="6" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="183" hidden="1" spans="3:3">
-      <c r="C183" s="12" t="s">
+    <row r="183" spans="1:4" hidden="1">
+      <c r="C183" s="6" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="184" hidden="1" spans="4:4">
-      <c r="D184" s="15" t="s">
+    <row r="184" spans="1:4" hidden="1">
+      <c r="D184" s="9" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="185" hidden="1"/>
-    <row r="186" hidden="1" spans="3:3">
-      <c r="C186" s="12" t="s">
+    <row r="185" spans="1:4" hidden="1"/>
+    <row r="186" spans="1:4" hidden="1">
+      <c r="C186" s="6" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="188" spans="1:2">
-      <c r="A188" s="11"/>
-      <c r="B188" s="11" t="s">
+    <row r="188" spans="1:4">
+      <c r="A188" s="5"/>
+      <c r="B188" s="5" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="189" spans="1:3">
-      <c r="A189" s="11"/>
-      <c r="B189" s="11"/>
-      <c r="C189" s="12" t="s">
+    <row r="189" spans="1:4">
+      <c r="A189" s="5"/>
+      <c r="B189" s="5"/>
+      <c r="C189" s="6" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="190" spans="1:2">
-      <c r="A190" s="11"/>
-      <c r="B190" s="11"/>
-    </row>
-    <row r="191" spans="1:2">
-      <c r="A191" s="11"/>
-      <c r="B191" s="11" t="s">
+    <row r="190" spans="1:4">
+      <c r="A190" s="5"/>
+      <c r="B190" s="5"/>
+    </row>
+    <row r="191" spans="1:4">
+      <c r="A191" s="5"/>
+      <c r="B191" s="5" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="192" spans="1:3">
-      <c r="A192" s="11"/>
-      <c r="B192" s="11"/>
-      <c r="C192" s="12" t="s">
+    <row r="192" spans="1:4">
+      <c r="A192" s="5"/>
+      <c r="B192" s="5"/>
+      <c r="C192" s="6" t="s">
         <v>236</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D87"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.25" defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="3" width="4" style="2" customWidth="1"/>
-    <col min="4" max="4" width="130.461538461538" style="3" customWidth="1"/>
-    <col min="5" max="16384" width="9.23076923076923" style="2"/>
+    <col min="4" max="4" width="130.5" style="3" customWidth="1"/>
+    <col min="5" max="16384" width="9.25" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12" t="s">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12" t="s">
+      <c r="A3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="12"/>
-      <c r="B5" s="11" t="s">
+      <c r="A5" s="6"/>
+      <c r="B5" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="C5" s="12"/>
-    </row>
-    <row r="6" spans="2:3">
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
+      <c r="C5" s="6"/>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="12"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="12"/>
-    </row>
-    <row r="21" spans="3:3">
+      <c r="A10" s="6"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="6"/>
+    </row>
+    <row r="21" spans="2:4">
       <c r="C21" s="2" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="22" spans="4:4">
+    <row r="22" spans="2:4">
       <c r="D22" s="3" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="23" spans="4:4">
+    <row r="23" spans="2:4">
       <c r="D23" s="3" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="25" spans="3:3">
+    <row r="25" spans="2:4">
       <c r="C25" s="2" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="26" spans="4:4">
+    <row r="26" spans="2:4">
       <c r="D26" s="3" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="27" spans="4:4">
+    <row r="27" spans="2:4">
       <c r="D27" s="3" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="29" spans="2:2">
-      <c r="B29" s="13" t="s">
+    <row r="29" spans="2:4">
+      <c r="B29" s="7" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="30" spans="4:4">
+    <row r="30" spans="2:4">
       <c r="D30" s="3" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="31" ht="31" spans="4:4">
+    <row r="31" spans="2:4" ht="31">
       <c r="D31" s="3" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="32" spans="4:4">
-      <c r="D32" s="14" t="s">
+    <row r="32" spans="2:4">
+      <c r="D32" s="8" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="33" spans="4:4">
-      <c r="D33" s="14" t="s">
+    <row r="33" spans="1:4">
+      <c r="D33" s="8" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="34" spans="4:4">
-      <c r="D34" s="14" t="s">
+    <row r="34" spans="1:4">
+      <c r="D34" s="8" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="35" spans="4:4">
-      <c r="D35" s="14" t="s">
+    <row r="35" spans="1:4">
+      <c r="D35" s="8" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="36" ht="31" spans="4:4">
+    <row r="36" spans="1:4" ht="31">
       <c r="D36" s="3" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="38" spans="2:2">
-      <c r="B38" s="13" t="s">
+    <row r="38" spans="1:4">
+      <c r="B38" s="7" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="39" spans="2:4">
-      <c r="B39" s="13"/>
+    <row r="39" spans="1:4">
+      <c r="B39" s="7"/>
       <c r="D39" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="40" ht="31" spans="4:4">
+    <row r="40" spans="1:4" ht="31">
       <c r="D40" s="3" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="42" ht="31" spans="4:4">
+    <row r="42" spans="1:4" ht="46.5">
       <c r="D42" s="3" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="13" t="s">
+      <c r="A43" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="B43" s="13" t="s">
+      <c r="B43" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="D43" s="14" t="s">
+      <c r="D43" s="8" t="s">
         <v>260</v>
       </c>
     </row>
@@ -4890,7 +4277,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="46" spans="2:4">
+    <row r="46" spans="1:4">
       <c r="B46" s="2" t="s">
         <v>268</v>
       </c>
@@ -4901,7 +4288,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="47" spans="2:4">
+    <row r="47" spans="1:4">
       <c r="B47" s="2" t="s">
         <v>271</v>
       </c>
@@ -4912,136 +4299,136 @@
         <v>273</v>
       </c>
     </row>
-    <row r="48" spans="4:4">
+    <row r="48" spans="1:4">
       <c r="D48" s="2" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="50" spans="2:2">
-      <c r="B50" s="13" t="s">
+    <row r="50" spans="2:4">
+      <c r="B50" s="7" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="51" ht="46.5" spans="4:4">
+    <row r="51" spans="2:4" ht="46.5">
       <c r="D51" s="3" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="53" spans="4:4">
-      <c r="D53" s="14" t="s">
+    <row r="53" spans="2:4">
+      <c r="D53" s="8" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="54" ht="62" spans="4:4">
+    <row r="54" spans="2:4" ht="77.5">
       <c r="D54" s="3" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="56" spans="4:4">
-      <c r="D56" s="14" t="s">
+    <row r="56" spans="2:4">
+      <c r="D56" s="8" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="57" ht="46.5" spans="4:4">
+    <row r="57" spans="2:4" ht="46.5">
       <c r="D57" s="3" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="59" ht="31" spans="4:4">
+    <row r="59" spans="2:4" ht="31">
       <c r="D59" s="3" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="60" spans="4:4">
+    <row r="60" spans="2:4">
       <c r="D60" s="3" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="62" spans="2:2">
-      <c r="B62" s="13" t="s">
+    <row r="62" spans="2:4">
+      <c r="B62" s="7" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="63" spans="2:3">
-      <c r="B63" s="13"/>
+    <row r="63" spans="2:4">
+      <c r="B63" s="7"/>
       <c r="C63" s="2" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="64" ht="46.5" spans="2:4">
-      <c r="B64" s="13"/>
+    <row r="64" spans="2:4" ht="46.5">
+      <c r="B64" s="7"/>
       <c r="D64" s="3" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="65" spans="2:4">
-      <c r="B65" s="13"/>
+      <c r="B65" s="7"/>
       <c r="D65" s="3" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="66" spans="2:4">
-      <c r="B66" s="13"/>
+      <c r="B66" s="7"/>
       <c r="D66" s="3" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="67" spans="2:4">
-      <c r="B67" s="13"/>
+      <c r="B67" s="7"/>
       <c r="D67" s="3" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="68" spans="2:4">
-      <c r="B68" s="13"/>
+      <c r="B68" s="7"/>
       <c r="D68" s="3" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="69" spans="2:2">
-      <c r="B69" s="13"/>
-    </row>
-    <row r="70" spans="2:2">
-      <c r="B70" s="13" t="s">
+    <row r="69" spans="2:4">
+      <c r="B69" s="7"/>
+    </row>
+    <row r="70" spans="2:4">
+      <c r="B70" s="7" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="71" spans="3:3">
+    <row r="71" spans="2:4">
       <c r="C71" s="2" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="72" spans="4:4">
-      <c r="D72" s="14" t="s">
+    <row r="72" spans="2:4">
+      <c r="D72" s="8" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="73" spans="4:4">
+    <row r="73" spans="2:4">
       <c r="D73" s="3" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="74" spans="4:4">
+    <row r="74" spans="2:4">
       <c r="D74" s="3" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="75" spans="4:4">
+    <row r="75" spans="2:4">
       <c r="D75" s="3" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="77" spans="4:4">
-      <c r="D77" s="14" t="s">
+    <row r="77" spans="2:4">
+      <c r="D77" s="8" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="78" spans="4:4">
+    <row r="78" spans="2:4">
       <c r="D78" s="3" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="79" ht="31" spans="4:4">
+    <row r="79" spans="2:4" ht="31">
       <c r="D79" s="3" t="s">
         <v>297</v>
       </c>
@@ -5056,7 +4443,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="83" spans="4:4">
+    <row r="83" spans="4:4" ht="31">
       <c r="D83" s="3" t="s">
         <v>300</v>
       </c>
@@ -5071,314 +4458,311 @@
         <v>302</v>
       </c>
     </row>
-    <row r="87" ht="31" spans="4:4">
+    <row r="87" spans="4:4" ht="31">
       <c r="D87" s="3" t="s">
         <v>303</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D238"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.25" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="3" width="3" style="5" customWidth="1"/>
-    <col min="4" max="4" width="156.923076923077" style="6" customWidth="1"/>
-    <col min="5" max="16384" width="9.23076923076923" style="5"/>
+    <col min="1" max="3" width="3" style="24" customWidth="1"/>
+    <col min="4" max="4" width="156.9140625" style="25" customWidth="1"/>
+    <col min="5" max="16384" width="9.25" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="23" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="2" spans="4:4">
-      <c r="D2" s="6" t="s">
+    <row r="2" spans="1:4">
+      <c r="D2" s="25" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="3" ht="46.5" spans="4:4">
-      <c r="D3" s="6" t="s">
+    <row r="3" spans="1:4" ht="42">
+      <c r="D3" s="25" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="7" t="s">
+    <row r="4" spans="1:4">
+      <c r="A4" s="23" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="5" spans="2:2">
-      <c r="B5" s="7" t="s">
+    <row r="5" spans="1:4">
+      <c r="B5" s="23" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="6" spans="3:3">
-      <c r="C6" s="5" t="s">
+    <row r="6" spans="1:4">
+      <c r="C6" s="24" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="7" spans="3:3">
-      <c r="C7" s="7" t="s">
+    <row r="7" spans="1:4">
+      <c r="C7" s="23" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="8" ht="31" spans="3:4">
-      <c r="C8" s="7"/>
-      <c r="D8" s="6" t="s">
+    <row r="8" spans="1:4" ht="28">
+      <c r="C8" s="23"/>
+      <c r="D8" s="25" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="9" ht="93" spans="3:4">
-      <c r="C9" s="7"/>
-      <c r="D9" s="8" t="s">
+    <row r="9" spans="1:4" ht="84">
+      <c r="C9" s="23"/>
+      <c r="D9" s="26" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="70">
+      <c r="C10" s="23"/>
+      <c r="D10" s="26" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="C11" s="23"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="C12" s="23" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="10" ht="77.5" spans="3:4">
-      <c r="C10" s="7"/>
-      <c r="D10" s="8" t="s">
+    <row r="13" spans="1:4" ht="28">
+      <c r="C13" s="23"/>
+      <c r="D13" s="25" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="11" spans="3:3">
-      <c r="C11" s="7"/>
-    </row>
-    <row r="12" spans="3:3">
-      <c r="C12" s="7" t="s">
+    <row r="14" spans="1:4" ht="84">
+      <c r="D14" s="26" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="70">
+      <c r="D15" s="26" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="42">
+      <c r="D17" s="26" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="C19" s="23" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="13" ht="31" spans="3:4">
-      <c r="C13" s="7"/>
-      <c r="D13" s="6" t="s">
+    <row r="20" spans="1:4">
+      <c r="D20" s="25" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="14" ht="93" spans="4:4">
-      <c r="D14" s="8" t="s">
+    <row r="22" spans="1:4">
+      <c r="C22" s="23" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="15" ht="77.5" spans="4:4">
-      <c r="D15" s="8" t="s">
+    <row r="23" spans="1:4">
+      <c r="D23" s="25" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="17" ht="46.5" spans="4:4">
-      <c r="D17" s="8" t="s">
+    <row r="24" spans="1:4">
+      <c r="A24" s="23"/>
+      <c r="B24" s="23"/>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="23"/>
+      <c r="B25" s="23" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="19" spans="3:3">
-      <c r="C19" s="7" t="s">
+    <row r="26" spans="1:4">
+      <c r="A26" s="23"/>
+      <c r="B26" s="23"/>
+      <c r="D26" s="25" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="20" spans="4:4">
-      <c r="D20" s="6" t="s">
+    <row r="27" spans="1:4">
+      <c r="A27" s="23"/>
+      <c r="B27" s="23"/>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="23"/>
+      <c r="B28" s="23" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="22" spans="3:3">
-      <c r="C22" s="7" t="s">
+    <row r="29" spans="1:4">
+      <c r="A29" s="23"/>
+      <c r="B29" s="23"/>
+      <c r="D29" s="25" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="23" spans="4:4">
-      <c r="D23" s="6" t="s">
+    <row r="30" spans="1:4">
+      <c r="A30" s="23"/>
+      <c r="B30" s="23"/>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="23"/>
+      <c r="B31" s="23" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7" t="s">
+    <row r="32" spans="1:4">
+      <c r="A32" s="23"/>
+      <c r="B32" s="23"/>
+      <c r="D32" s="25" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="D26" s="6" t="s">
+    <row r="33" spans="1:4">
+      <c r="A33" s="23"/>
+      <c r="B33" s="23"/>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="23"/>
+      <c r="B34" s="23" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7" t="s">
+    <row r="35" spans="1:4">
+      <c r="A35" s="23"/>
+      <c r="B35" s="23"/>
+      <c r="D35" s="25" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="D29" s="6" t="s">
+    <row r="36" spans="1:4">
+      <c r="A36" s="23"/>
+      <c r="B36" s="23"/>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="23"/>
+      <c r="B37" s="23" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="7"/>
-      <c r="B31" s="7" t="s">
+    <row r="38" spans="1:4">
+      <c r="A38" s="23"/>
+      <c r="B38" s="23"/>
+      <c r="D38" s="25" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
-      <c r="D32" s="6" t="s">
+    <row r="39" spans="1:4">
+      <c r="A39" s="23"/>
+      <c r="B39" s="23"/>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="23"/>
+      <c r="B40" s="23"/>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="23" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="7"/>
-      <c r="B34" s="7" t="s">
+      <c r="B41" s="23"/>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="23"/>
+      <c r="B42" s="23" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
-      <c r="A35" s="7"/>
-      <c r="B35" s="7"/>
-      <c r="D35" s="6" t="s">
+    <row r="43" spans="1:4">
+      <c r="C43" s="24" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="7"/>
-      <c r="B36" s="7"/>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="7"/>
-      <c r="B37" s="7" t="s">
+    <row r="44" spans="1:4">
+      <c r="D44" s="25" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
-      <c r="A38" s="7"/>
-      <c r="B38" s="7"/>
-      <c r="D38" s="6" t="s">
+    <row r="45" spans="1:4" ht="84">
+      <c r="D45" s="25" t="s">
         <v>332</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="7"/>
-      <c r="B39" s="7"/>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="7"/>
-      <c r="B40" s="7"/>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="7" t="s">
+    <row r="231" spans="1:4">
+      <c r="A231" s="23" t="s">
         <v>333</v>
       </c>
-      <c r="B41" s="9"/>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="9"/>
-      <c r="B42" s="7" t="s">
+      <c r="B231" s="23"/>
+      <c r="C231" s="23"/>
+      <c r="D231" s="26" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="43" spans="3:3">
-      <c r="C43" s="10" t="s">
+    <row r="232" spans="1:4">
+      <c r="A232" s="24" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="44" spans="3:4">
-      <c r="C44" s="10"/>
-      <c r="D44" s="6" t="s">
+      <c r="D232" s="25" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="45" ht="93" spans="4:4">
-      <c r="D45" s="6" t="s">
+    <row r="233" spans="1:4" ht="42">
+      <c r="A233" s="27" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="231" spans="1:4">
-      <c r="A231" s="7" t="s">
+      <c r="B233" s="27"/>
+      <c r="C233" s="27"/>
+      <c r="D233" s="25" t="s">
         <v>338</v>
       </c>
-      <c r="B231" s="7"/>
-      <c r="C231" s="7"/>
-      <c r="D231" s="8" t="s">
+    </row>
+    <row r="234" spans="1:4" ht="42">
+      <c r="A234" s="27" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="232" spans="1:4">
-      <c r="A232" s="5" t="s">
+      <c r="B234" s="27"/>
+      <c r="C234" s="27"/>
+      <c r="D234" s="25" t="s">
         <v>340</v>
       </c>
-      <c r="D232" s="6" t="s">
+    </row>
+    <row r="236" spans="1:4">
+      <c r="A236" s="23" t="s">
         <v>341</v>
       </c>
-    </row>
-    <row r="233" ht="31" spans="1:4">
-      <c r="A233" s="6" t="s">
+      <c r="B236" s="23"/>
+      <c r="C236" s="23"/>
+      <c r="D236" s="26" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4">
+      <c r="A237" s="24" t="s">
         <v>342</v>
       </c>
-      <c r="B233" s="6"/>
-      <c r="C233" s="6"/>
-      <c r="D233" s="6" t="s">
+      <c r="D237" s="25" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="234" ht="46.5" spans="1:4">
-      <c r="A234" s="6" t="s">
+    <row r="238" spans="1:4">
+      <c r="A238" s="24" t="s">
         <v>344</v>
       </c>
-      <c r="B234" s="6"/>
-      <c r="C234" s="6"/>
-      <c r="D234" s="6" t="s">
+      <c r="D238" s="25" t="s">
         <v>345</v>
-      </c>
-    </row>
-    <row r="236" spans="1:4">
-      <c r="A236" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="B236" s="7"/>
-      <c r="C236" s="7"/>
-      <c r="D236" s="8" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="237" spans="1:4">
-      <c r="A237" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="D237" s="6" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="238" spans="1:4">
-      <c r="A238" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="D238" s="6" t="s">
-        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -5388,295 +4772,290 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A5:E26"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.25" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="3" width="1.84615384615385" customWidth="1"/>
-    <col min="4" max="4" width="2.07692307692308" customWidth="1"/>
-    <col min="5" max="5" width="156.769230769231" customWidth="1"/>
+    <col min="1" max="3" width="1.83203125" customWidth="1"/>
+    <col min="4" max="4" width="2.08203125" customWidth="1"/>
+    <col min="5" max="5" width="156.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:5">
       <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:5">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:5">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="9" ht="201.5" spans="1:5">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="195">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="4" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="10" ht="93" spans="5:5">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="90">
       <c r="E10" s="4" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="25" spans="3:3">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="25" spans="3:4">
       <c r="C25" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="26" spans="4:4">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="26" spans="3:4">
       <c r="D26" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B1:D15"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9.25" defaultRowHeight="15.5"/>
   <cols>
-    <col min="1" max="1" width="2.76923076923077" style="2" customWidth="1"/>
-    <col min="2" max="2" width="2.61538461538462" style="2" customWidth="1"/>
-    <col min="3" max="3" width="3.23076923076923" style="2" customWidth="1"/>
-    <col min="4" max="4" width="153.615384615385" style="3" customWidth="1"/>
-    <col min="5" max="16384" width="9.23076923076923" style="2"/>
+    <col min="1" max="1" width="2.75" style="2" customWidth="1"/>
+    <col min="2" max="2" width="2.58203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="3.25" style="2" customWidth="1"/>
+    <col min="4" max="4" width="153.58203125" style="3" customWidth="1"/>
+    <col min="5" max="16384" width="9.25" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2">
+    <row r="1" spans="2:4">
       <c r="B1" s="2" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="2" spans="2:4">
+      <c r="C2" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" ht="31">
+      <c r="D5" s="3" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="46.5">
+      <c r="D7" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="31">
+      <c r="D9" s="3" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4">
+      <c r="D11" s="3" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="2" spans="3:3">
-      <c r="C2" s="2" t="s">
+    <row r="13" spans="2:4" ht="31">
+      <c r="D13" s="3" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="5" ht="31" spans="4:4">
-      <c r="D5" s="3" t="s">
+    <row r="14" spans="2:4" ht="16" customHeight="1">
+      <c r="D14" s="3" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="7" ht="31" spans="4:4">
-      <c r="D7" s="3" t="s">
+    <row r="15" spans="2:4">
+      <c r="D15" s="3" t="s">
         <v>361</v>
-      </c>
-    </row>
-    <row r="9" ht="31" spans="4:4">
-      <c r="D9" s="3" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="11" spans="4:4">
-      <c r="D11" s="3" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="13" ht="31" spans="4:4">
-      <c r="D13" s="3" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="14" ht="16" customHeight="1" spans="4:4">
-      <c r="D14" s="3" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="15" spans="4:4">
-      <c r="D15" s="3" t="s">
-        <v>366</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:E46"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9.25" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="4" width="2.76923076923077" style="1" customWidth="1"/>
-    <col min="5" max="5" width="99.6384615384615" customWidth="1"/>
+    <col min="1" max="4" width="2.75" style="21" customWidth="1"/>
+    <col min="5" max="5" width="99.6640625" style="22" customWidth="1"/>
+    <col min="6" max="16384" width="9.25" style="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="21" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="B3" s="21" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="E4" s="22" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="B6" s="21" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="E7" s="22" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="E8" s="22" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="B10" s="21" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="3" spans="2:2">
-      <c r="B3" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="4" spans="5:5">
-      <c r="E4" t="s">
+    <row r="11" spans="1:5">
+      <c r="E11" s="22" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="6" spans="2:2">
-      <c r="B6" s="1" t="s">
+    <row r="12" spans="1:5">
+      <c r="E12" s="22" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="7" spans="5:5">
-      <c r="E7" t="s">
+    <row r="13" spans="1:5">
+      <c r="E13" s="22" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="8" spans="5:5">
-      <c r="E8" t="s">
+    <row r="14" spans="1:5">
+      <c r="E14" s="22" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="10" spans="2:2">
-      <c r="B10" s="1" t="s">
+    <row r="15" spans="1:5">
+      <c r="E15" s="22" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="11" spans="5:5">
-      <c r="E11" t="s">
+    <row r="16" spans="1:5">
+      <c r="E16" s="22" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="12" spans="5:5">
-      <c r="E12" t="s">
+    <row r="18" spans="2:5">
+      <c r="E18" s="22" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="13" spans="5:5">
-      <c r="E13" t="s">
+    <row r="19" spans="2:5">
+      <c r="E19" s="22" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="14" spans="5:5">
-      <c r="E14" t="s">
+    <row r="20" spans="2:5">
+      <c r="D20" s="21" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5">
+      <c r="E21" s="22" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="15" spans="5:5">
-      <c r="E15" t="s">
+    <row r="22" spans="2:5">
+      <c r="E22" s="22" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="16" spans="5:5">
-      <c r="E16" t="s">
+    <row r="23" spans="2:5">
+      <c r="E23" s="22" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="18" spans="5:5">
-      <c r="E18" t="s">
+    <row r="25" spans="2:5">
+      <c r="E25" s="22" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="19" spans="5:5">
-      <c r="E19" t="s">
+    <row r="27" spans="2:5">
+      <c r="D27" s="21" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="20" spans="4:4">
-      <c r="D20" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="21" spans="5:5">
-      <c r="E21" t="s">
+    <row r="28" spans="2:5">
+      <c r="E28" s="22" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="22" spans="5:5">
-      <c r="E22" t="s">
+    <row r="30" spans="2:5">
+      <c r="B30" s="21" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="23" spans="5:5">
-      <c r="E23" t="s">
+    <row r="43" spans="4:5">
+      <c r="D43" s="22" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="25" spans="5:5">
-      <c r="E25" t="s">
+    <row r="44" spans="4:5">
+      <c r="E44" s="22" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="27" spans="4:4">
-      <c r="D27" s="1" t="s">
+    <row r="45" spans="4:5">
+      <c r="E45" s="22" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="28" spans="5:5">
-      <c r="E28" t="s">
+    <row r="46" spans="4:5">
+      <c r="E46" s="22" t="s">
         <v>386</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2">
-      <c r="B30" s="1" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="43" spans="4:4">
-      <c r="D43" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="44" spans="5:5">
-      <c r="E44" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="45" spans="5:5">
-      <c r="E45" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="46" spans="5:5">
-      <c r="E46" t="s">
-        <v>391</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-  <drawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>